--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EffectInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -192,6 +192,18 @@
   </si>
   <si>
     <t>冰锥</t>
+  </si>
+  <si>
+    <t>EffectThunder_1</t>
+  </si>
+  <si>
+    <t>雷电连锁1</t>
+  </si>
+  <si>
+    <t>EffectThunder_2</t>
+  </si>
+  <si>
+    <t>雷电连锁2</t>
   </si>
 </sst>
 </file>
@@ -1483,6 +1495,40 @@
         <v>54</v>
       </c>
     </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>900001</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>900002</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0.5</v>
+      </c>
+      <c r="J15" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="19" ht="12" customHeight="1"/>
     <row r="20" ht="12" customHeight="1"/>
     <row r="21" ht="12" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1325,44 +1325,41 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="n">
-        <v>500001</v>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>EffectBuff_1</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>LifeTime:0.5&amp;Size:1</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>StartPosition:{StartPosition}</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>ColorFloor:0.451,0.972,0.407,1&amp;ColorGlowV:0.198,0.734,0.156,1&amp;ColorLine:0.376,1.474,0.313,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:1,0.949,0.580,1</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
-        <is>
-          <t>加血</t>
+      <c r="A8" t="n">
+        <v>400002</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EffectSlash_1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LifeTime:0.2&amp;Size:1&amp;Speed:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Direction:{Direction}</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BOSS刀锋-远距离(前方6格)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
@@ -1387,78 +1384,86 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>ColorFloor:0.636,1,0.996,1&amp;ColorGlowV:0.325,0.657,1,1&amp;ColorLine:0.686,0.992,0.958,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:0.505,1,0.845,1</t>
+          <t>ColorFloor:0.451,0.972,0.407,1&amp;ColorGlowV:0.198,0.734,0.156,1&amp;ColorLine:0.376,1.474,0.313,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:1,0.949,0.580,1</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>加甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>EffectBuff_2</t>
+          <t>EffectBuff_1</t>
         </is>
       </c>
       <c r="C10" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>LifeTime:0.5&amp;Size:1</t>
+        </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+          <t>StartPosition:{StartPosition}</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
+          <t>ColorFloor:0.636,1,0.996,1&amp;ColorGlowV:0.325,0.657,1,1&amp;ColorLine:0.686,0.992,0.958,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:0.505,1,0.845,1</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>魅惑</t>
+          <t>加甲</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>EffectBodySlam_1</t>
+          <t>EffectBuff_2</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>Size:0.75*{Size}</t>
-        </is>
-      </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:{StartPosition}</t>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
         </is>
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>地面打击</t>
+          <t>魅惑</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>800001</v>
+        <v>700001</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>EffectPillarBlast_Fire_1</t>
+          <t>EffectBodySlam_1</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>Size:1.25*{Size}</t>
+          <t>Size:0.75*{Size}</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -1476,17 +1481,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>火锥</t>
+          <t>地面打击</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>EffectPillarBlast_Ice_1</t>
+          <t>EffectPillarBlast_Fire_1</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
@@ -1504,38 +1509,45 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>冰锥</t>
+          <t>火锥</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>900001</v>
+        <v>800002</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>EffectThunder_1</t>
+          <t>EffectPillarBlast_Ice_1</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Size:1.25*{Size}</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>StartPosition:{StartPosition}</t>
+        </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁1</t>
+          <t>冰锥</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>EffectThunder_2</t>
+          <t>EffectThunder_1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
@@ -1546,38 +1558,38 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁2</t>
+          <t>雷电连锁1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>1000001</v>
+        <v>900002</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Effect_Mana_1</t>
+          <t>EffectThunder_2</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-魔王消耗魔力</t>
+          <t>雷电连锁2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>1100001</v>
+        <v>1000001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Effect_CreatureShow_1</t>
+          <t>Effect_Mana_1</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
@@ -1588,38 +1600,38 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-生成登场</t>
+          <t>放置魔物-魔王消耗魔力</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>1200001</v>
+        <v>1100001</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>EffectBlood_1</t>
+          <t>Effect_CreatureShow_1</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>受击溅血(高频)</t>
+          <t>放置魔物-生成登场</t>
         </is>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>1300001</v>
+        <v>1200001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>EffectShieldHit_1</t>
+          <t>EffectBlood_1</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
@@ -1630,17 +1642,17 @@
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>护盾打击(高频)</t>
+          <t>受击溅血(高频)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>1400001</v>
+        <v>1300001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>EffectMove_1</t>
+          <t>EffectShieldHit_1</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
@@ -1651,32 +1663,52 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
+          <t>护盾打击(高频)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="12" customHeight="1" s="1">
+      <c r="A21" s="0" t="n">
+        <v>1400001</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>EffectMove_1</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
           <t>进阶增加进度</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="12" customHeight="1" s="1">
-      <c r="A21" t="n">
+    <row r="22" ht="12" customHeight="1" s="1">
+      <c r="A22" s="0" t="n">
         <v>1500001</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>EffectAscendComplete_1</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>进阶完成庆祝</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="12" customHeight="1" s="1"/>
     <row r="23" ht="12" customHeight="1" s="1"/>
     <row r="24" ht="12" customHeight="1" s="1"/>
     <row r="25" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1325,33 +1325,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>400002</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>EffectSlash_1</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>LifeTime:0.2&amp;Size:1&amp;Speed:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>Direction:{Direction}</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>StartPosition:0,0.5,0+{StartPosition}</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>BOSS刀锋-远距离(前方6格)</t>
         </is>
@@ -1709,7 +1709,27 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="12" customHeight="1" s="1"/>
+    <row r="23" ht="12" customHeight="1" s="1">
+      <c r="A23" t="n">
+        <v>1600001</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Effect_Trail_1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>攻击弹道拖尾(方案2 VFX)</t>
+        </is>
+      </c>
+    </row>
     <row r="24" ht="12" customHeight="1" s="1"/>
     <row r="25" ht="12" customHeight="1" s="1"/>
     <row r="26" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>EffectThunder_1</t>
+          <t>Effect_Thunder_1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>EffectThunder_2</t>
+          <t>Effect_Thunder_2</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
@@ -1585,32 +1585,32 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>1000001</v>
+        <v>900003</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Effect_Mana_1</t>
+          <t>Effect_Thunder_3</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-魔王消耗魔力</t>
+          <t>落雷(全局单例,深渊馈赠闪电)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>1100001</v>
+        <v>1000001</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Effect_CreatureShow_1</t>
+          <t>Effect_Mana_1</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
@@ -1621,38 +1621,38 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-生成登场</t>
+          <t>放置魔物-魔王消耗魔力</t>
         </is>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>1200001</v>
+        <v>1100001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>EffectBlood_1</t>
+          <t>Effect_CreatureShow_1</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>受击溅血(高频)</t>
+          <t>放置魔物-生成登场</t>
         </is>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>1300001</v>
+        <v>1200001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>EffectShieldHit_1</t>
+          <t>EffectBlood_1</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>护盾打击(高频)</t>
+          <t>受击溅血(高频)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>1400001</v>
+        <v>1300001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>EffectMove_1</t>
+          <t>EffectShieldHit_1</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
@@ -1684,53 +1684,73 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>进阶增加进度</t>
+          <t>护盾打击(高频)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
+        <v>1400001</v>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>EffectMove_1</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>进阶增加进度</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1" s="1">
+      <c r="A23" s="0" t="n">
         <v>1500001</v>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>EffectAscendComplete_1</t>
         </is>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C23" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D23" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>进阶完成庆祝</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="12" customHeight="1" s="1">
-      <c r="A23" t="n">
+    <row r="24" ht="12" customHeight="1" s="1">
+      <c r="A24" s="0" t="n">
         <v>1600001</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Effect_Trail_1</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>攻击弹道拖尾(方案2 VFX)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="12" customHeight="1" s="1"/>
     <row r="25" ht="12" customHeight="1" s="1"/>
     <row r="26" ht="12" customHeight="1" s="1"/>
     <row r="27" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1751,8 +1751,53 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="12" customHeight="1" s="1"/>
-    <row r="26" ht="12" customHeight="1" s="1"/>
+    <row r="25" ht="12" customHeight="1" s="1">
+      <c r="A25" s="0" t="n">
+        <v>1700001</v>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Shockwave_1</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1" s="1">
+      <c r="A26" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Effect_FloorFire_1</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr"/>
+      <c r="F26" s="0" t="inlineStr"/>
+      <c r="G26" s="0" t="inlineStr"/>
+      <c r="H26" s="0" t="inlineStr"/>
+      <c r="I26" s="0" t="inlineStr"/>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowFloorFireEffect按燃烧时长重设主粒子duration)</t>
+        </is>
+      </c>
+    </row>
     <row r="27" ht="12" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>EffectSlash_1</t>
+          <t>Effect_Slash_1</t>
         </is>
       </c>
       <c r="C7" s="0" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>EffectSlash_1</t>
+          <t>Effect_Slash_1</t>
         </is>
       </c>
       <c r="C8" s="0" t="n">
@@ -1359,43 +1359,33 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>500001</v>
+        <v>400003</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>EffectBuff_1</t>
+          <t>Effect_Slash_2</t>
         </is>
       </c>
       <c r="C9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>LifeTime:0.5&amp;Size:1</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>StartPosition:{StartPosition}</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>ColorFloor:0.451,0.972,0.407,1&amp;ColorGlowV:0.198,0.734,0.156,1&amp;ColorLine:0.376,1.474,0.313,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:1,0.949,0.580,1</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>刀锋-新粒子(PS)(战之魅魔4001攻击)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
@@ -1420,78 +1410,86 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>ColorFloor:0.636,1,0.996,1&amp;ColorGlowV:0.325,0.657,1,1&amp;ColorLine:0.686,0.992,0.958,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:0.505,1,0.845,1</t>
+          <t>ColorFloor:0.451,0.972,0.407,1&amp;ColorGlowV:0.198,0.734,0.156,1&amp;ColorLine:0.376,1.474,0.313,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:1,0.949,0.580,1</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>加甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>EffectBuff_2</t>
+          <t>EffectBuff_1</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>LifeTime:0.5&amp;Size:1</t>
+        </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+          <t>StartPosition:{StartPosition}</t>
         </is>
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
+          <t>ColorFloor:0.636,1,0.996,1&amp;ColorGlowV:0.325,0.657,1,1&amp;ColorLine:0.686,0.992,0.958,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:0.505,1,0.845,1</t>
         </is>
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>魅惑</t>
+          <t>加甲</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>EffectBodySlam_1</t>
+          <t>EffectBuff_2</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>Size:0.75*{Size}</t>
-        </is>
-      </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:{StartPosition}</t>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>地面打击</t>
+          <t>魅惑</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>800001</v>
+        <v>700001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>EffectPillarBlast_Fire_1</t>
+          <t>EffectBodySlam_1</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
@@ -1499,7 +1497,7 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>Size:1.25*{Size}</t>
+          <t>Size:0.75*{Size}</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -1509,17 +1507,17 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>火锥</t>
+          <t>地面打击</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>EffectPillarBlast_Ice_1</t>
+          <t>EffectPillarBlast_Fire_1</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
@@ -1537,38 +1535,45 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>冰锥</t>
+          <t>火锥</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>900001</v>
+        <v>800002</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_1</t>
+          <t>EffectPillarBlast_Ice_1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Size:1.25*{Size}</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>StartPosition:{StartPosition}</t>
+        </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁1</t>
+          <t>冰锥</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_2</t>
+          <t>Effect_Thunder_1</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
@@ -1579,59 +1584,59 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁2</t>
+          <t>雷电连锁1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>900003</v>
+        <v>900002</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_3</t>
+          <t>Effect_Thunder_2</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>落雷(全局单例,深渊馈赠闪电)</t>
+          <t>雷电连锁2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>1000001</v>
+        <v>900003</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Effect_Mana_1</t>
+          <t>Effect_Thunder_3</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-魔王消耗魔力</t>
+          <t>落雷(全局单例,深渊馈赠闪电)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>1100001</v>
+        <v>1000001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Effect_CreatureShow_1</t>
+          <t>Effect_Mana_1</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
@@ -1642,38 +1647,38 @@
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-生成登场</t>
+          <t>放置魔物-魔王消耗魔力</t>
         </is>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>1200001</v>
+        <v>1100001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>EffectBlood_1</t>
+          <t>Effect_CreatureShow_1</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>受击溅血(高频)</t>
+          <t>放置魔物-生成登场</t>
         </is>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>1300001</v>
+        <v>1200001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>EffectShieldHit_1</t>
+          <t>EffectBlood_1</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
@@ -1684,17 +1689,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>护盾打击(高频)</t>
+          <t>受击溅血(高频)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>1400001</v>
+        <v>1300001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>EffectMove_1</t>
+          <t>EffectShieldHit_1</t>
         </is>
       </c>
       <c r="C22" s="0" t="n">
@@ -1705,100 +1710,120 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>进阶增加进度</t>
+          <t>护盾打击(高频)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="1">
       <c r="A23" s="0" t="n">
-        <v>1500001</v>
+        <v>1400001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>EffectAscendComplete_1</t>
+          <t>EffectMove_1</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>进阶完成庆祝</t>
+          <t>进阶增加进度</t>
         </is>
       </c>
     </row>
     <row r="24" ht="12" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>1600001</v>
+        <v>1500001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Effect_Trail_1</t>
+          <t>EffectAscendComplete_1</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>攻击弹道拖尾(方案2 VFX)</t>
+          <t>进阶完成庆祝</t>
         </is>
       </c>
     </row>
     <row r="25" ht="12" customHeight="1" s="1">
       <c r="A25" s="0" t="n">
-        <v>1700001</v>
+        <v>1600001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Effect_Shockwave_1</t>
+          <t>Effect_Trail_1</t>
         </is>
       </c>
       <c r="C25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="0" t="n">
-        <v>4</v>
-      </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+          <t>攻击弹道拖尾(方案2 VFX)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="12" customHeight="1" s="1">
       <c r="A26" s="0" t="n">
+        <v>1700001</v>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Shockwave_1</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="12" customHeight="1" s="1">
+      <c r="A27" s="0" t="n">
         <v>1800001</v>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Effect_FloorFire_1</t>
         </is>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D27" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="E26" s="0" t="inlineStr"/>
-      <c r="F26" s="0" t="inlineStr"/>
-      <c r="G26" s="0" t="inlineStr"/>
-      <c r="H26" s="0" t="inlineStr"/>
-      <c r="I26" s="0" t="inlineStr"/>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr"/>
+      <c r="F27" s="0" t="inlineStr"/>
+      <c r="G27" s="0" t="inlineStr"/>
+      <c r="H27" s="0" t="inlineStr"/>
+      <c r="I27" s="0" t="inlineStr"/>
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowFloorFireEffect按燃烧时长重设主粒子duration)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="12" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1820,7 +1820,7 @@
       <c r="I27" s="0" t="inlineStr"/>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowFloorFireEffect按燃烧时长重设主粒子duration)</t>
+          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowEnduringSingletonEffect(effect_hit击中粒子1800001)按燃烧时长重设主粒子duration)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>EffectBoom_Fire_1</t>
+          <t>Effect_Boom_Fire_1</t>
         </is>
       </c>
       <c r="C4" s="0" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>EffectBoom_Ice_1</t>
+          <t>Effect_Boom_Ice_1</t>
         </is>
       </c>
       <c r="C5" s="0" t="n">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>EffectExplosion_1</t>
+          <t>Effect_Explosion_1</t>
         </is>
       </c>
       <c r="C6" s="0" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>EffectBuff_1</t>
+          <t>Effect_Buff_Health_1</t>
         </is>
       </c>
       <c r="C10" s="0" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>EffectBuff_1</t>
+          <t>Effect_Buff_1</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>EffectBuff_2</t>
+          <t>Effect_Buff_2</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>EffectBodySlam_1</t>
+          <t>Effect_BodySlam_1</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>EffectPillarBlast_Fire_1</t>
+          <t>Effect_PillarBlast_Fire_1</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>EffectPillarBlast_Ice_1</t>
+          <t>Effect_PillarBlast_Ice_1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>EffectBlood_1</t>
+          <t>Effect_Blood_1</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>EffectShieldHit_1</t>
+          <t>Effect_ShieldHit_1</t>
         </is>
       </c>
       <c r="C22" s="0" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>EffectMove_1</t>
+          <t>Effect_Move_1</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>EffectAscendComplete_1</t>
+          <t>Effect_AscendComplete_1</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1824,6 +1824,24 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1900001</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Effect_Hit_1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>击中(通用,牛头人投手落点)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1292,41 +1292,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n">
-        <v>400001</v>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>Effect_Slash_1</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="A7" t="n">
+        <v>300002</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Effect_Explosion_2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>LifeTime:0.2&amp;Size:1&amp;Speed:10</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>Direction:{Direction}</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>StartPosition:0,0.5,0+{StartPosition}</t>
-        </is>
-      </c>
-      <c r="J7" s="0" t="inlineStr">
-        <is>
-          <t>刀锋</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>爆炸2(自爆史莱姆/哥布林敢死队,全局单例)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
@@ -1338,7 +1323,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>LifeTime:0.2&amp;Size:1&amp;Speed:30</t>
+          <t>LifeTime:0.2&amp;Size:1&amp;Speed:10</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -1353,79 +1338,76 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>BOSS刀锋-远距离(前方6格)</t>
+          <t>刀锋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>400003</v>
+        <v>400002</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Effect_Slash_2</t>
+          <t>Effect_Slash_1</t>
         </is>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr"/>
-      <c r="F9" s="0" t="inlineStr"/>
-      <c r="G9" s="0" t="inlineStr"/>
-      <c r="H9" s="0" t="inlineStr"/>
-      <c r="I9" s="0" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>LifeTime:0.2&amp;Size:1&amp;Speed:30</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Direction:{Direction}</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>刀锋-新粒子(PS)(战之魅魔4001攻击)</t>
+          <t>BOSS刀锋-远距离(前方6格)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>500001</v>
+        <v>400003</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Effect_Buff_Health_1</t>
+          <t>Effect_Slash_2</t>
         </is>
       </c>
       <c r="C10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>LifeTime:0.5&amp;Size:1</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>StartPosition:{StartPosition}</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>ColorFloor:0.451,0.972,0.407,1&amp;ColorGlowV:0.198,0.734,0.156,1&amp;ColorLine:0.376,1.474,0.313,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:1,0.949,0.580,1</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>刀锋-新粒子(PS)(战之魅魔4001攻击)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Effect_Buff_1</t>
+          <t>Effect_Buff_Health_1</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
@@ -1446,78 +1428,86 @@
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>ColorFloor:0.636,1,0.996,1&amp;ColorGlowV:0.325,0.657,1,1&amp;ColorLine:0.686,0.992,0.958,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:0.505,1,0.845,1</t>
+          <t>ColorFloor:0.451,0.972,0.407,1&amp;ColorGlowV:0.198,0.734,0.156,1&amp;ColorLine:0.376,1.474,0.313,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:1,0.949,0.580,1</t>
         </is>
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>加甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Effect_Buff_2</t>
+          <t>Effect_Buff_1</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>LifeTime:0.5&amp;Size:1</t>
+        </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+          <t>StartPosition:{StartPosition}</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
+          <t>ColorFloor:0.636,1,0.996,1&amp;ColorGlowV:0.325,0.657,1,1&amp;ColorLine:0.686,0.992,0.958,1&amp;ColorPoints:1,1,1,1&amp;ColorBoke:0.505,1,0.845,1</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>魅惑</t>
+          <t>加甲</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Effect_BodySlam_1</t>
+          <t>Effect_Buff_2</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>Size:0.75*{Size}</t>
-        </is>
-      </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:{StartPosition}</t>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>地面打击</t>
+          <t>魅惑</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>800001</v>
+        <v>700001</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Effect_PillarBlast_Fire_1</t>
+          <t>Effect_BodySlam_1</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
@@ -1525,7 +1515,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>Size:1.25*{Size}</t>
+          <t>Size:0.75*{Size}</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -1535,17 +1525,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>火锥</t>
+          <t>地面打击</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Effect_PillarBlast_Ice_1</t>
+          <t>Effect_PillarBlast_Fire_1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
@@ -1563,38 +1553,45 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>冰锥</t>
+          <t>火锥</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>900001</v>
+        <v>800002</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_1</t>
+          <t>Effect_PillarBlast_Ice_1</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Size:1.25*{Size}</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>StartPosition:{StartPosition}</t>
+        </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁1</t>
+          <t>冰锥</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_2</t>
+          <t>Effect_Thunder_1</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
@@ -1605,59 +1602,59 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁2</t>
+          <t>雷电连锁1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>900003</v>
+        <v>900002</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_3</t>
+          <t>Effect_Thunder_2</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>落雷(全局单例,深渊馈赠闪电)</t>
+          <t>雷电连锁2</t>
         </is>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>1000001</v>
+        <v>900003</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Effect_Mana_1</t>
+          <t>Effect_Thunder_3</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-魔王消耗魔力</t>
+          <t>落雷(全局单例,深渊馈赠闪电)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>1100001</v>
+        <v>1000001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Effect_CreatureShow_1</t>
+          <t>Effect_Mana_1</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
@@ -1668,38 +1665,38 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-生成登场</t>
+          <t>放置魔物-魔王消耗魔力</t>
         </is>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>1200001</v>
+        <v>1100001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>Effect_Blood_1</t>
+          <t>Effect_CreatureShow_1</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>受击溅血(高频)</t>
+          <t>放置魔物-生成登场</t>
         </is>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>1300001</v>
+        <v>1200001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Effect_ShieldHit_1</t>
+          <t>Effect_Blood_1</t>
         </is>
       </c>
       <c r="C22" s="0" t="n">
@@ -1710,17 +1707,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>护盾打击(高频)</t>
+          <t>受击溅血(高频)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="1">
       <c r="A23" s="0" t="n">
-        <v>1400001</v>
+        <v>1300001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>Effect_Move_1</t>
+          <t>Effect_ShieldHit_1</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
@@ -1731,112 +1728,133 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>进阶增加进度</t>
+          <t>护盾打击(高频)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="12" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>1500001</v>
+        <v>1400001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Effect_AscendComplete_1</t>
+          <t>Effect_Move_1</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>进阶完成庆祝</t>
+          <t>进阶增加进度</t>
         </is>
       </c>
     </row>
     <row r="25" ht="12" customHeight="1" s="1">
       <c r="A25" s="0" t="n">
-        <v>1600001</v>
+        <v>1500001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Effect_Trail_1</t>
+          <t>Effect_AscendComplete_1</t>
         </is>
       </c>
       <c r="C25" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>攻击弹道拖尾(方案2 VFX)</t>
+          <t>进阶完成庆祝</t>
         </is>
       </c>
     </row>
     <row r="26" ht="12" customHeight="1" s="1">
       <c r="A26" s="0" t="n">
-        <v>1700001</v>
+        <v>1600001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>Effect_Shockwave_1</t>
+          <t>Effect_Trail_1</t>
         </is>
       </c>
       <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="0" t="n">
-        <v>4</v>
-      </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+          <t>攻击弹道拖尾(方案2 VFX)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
+        <v>1700001</v>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Shockwave_1</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="n">
         <v>1800001</v>
       </c>
-      <c r="B27" s="0" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Effect_FloorFire_1</t>
         </is>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D28" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="E27" s="0" t="inlineStr"/>
-      <c r="F27" s="0" t="inlineStr"/>
-      <c r="G27" s="0" t="inlineStr"/>
-      <c r="H27" s="0" t="inlineStr"/>
-      <c r="I27" s="0" t="inlineStr"/>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr"/>
+      <c r="F28" s="0" t="inlineStr"/>
+      <c r="G28" s="0" t="inlineStr"/>
+      <c r="H28" s="0" t="inlineStr"/>
+      <c r="I28" s="0" t="inlineStr"/>
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowEnduringSingletonEffect(effect_hit击中粒子1800001)按燃烧时长重设主粒子duration)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="29">
+      <c r="A29" s="0" t="n">
         <v>1900001</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>Effect_Hit_1</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C29" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>击中(通用,牛头人投手落点)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1292,18 +1292,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>300002</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Effect_Explosion_2</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>爆炸2(自爆史莱姆/哥布林敢死队,全局单例)</t>
         </is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>LifeTime:0.2&amp;Size:1&amp;Speed:10</t>
+          <t>LifeTime:0.2&amp;Size:1&amp;Speed:5</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>刀锋</t>
+          <t>刀锋(前方1格,人类战士1001攻击)</t>
         </is>
       </c>
     </row>
@@ -1469,73 +1469,66 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>加甲</t>
+          <t>魅惑(4003引诱600001)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>600001</v>
+        <v>500003</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Effect_Buff_2</t>
+          <t>Effect_Buff_Def_1</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>StartPosition:0,0.5,0+{StartPosition}</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
-        </is>
+      <c r="D13" s="0" t="n">
+        <v>-1</v>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>魅惑</t>
+          <t>加甲(盾之魅魔4005,全局单例)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Effect_BodySlam_1</t>
+          <t>Effect_Buff_2</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>Size:0.75*{Size}</t>
-        </is>
-      </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:{StartPosition}</t>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>地面打击</t>
+          <t>魅惑</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>800001</v>
+        <v>700001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Effect_PillarBlast_Fire_1</t>
+          <t>Effect_BodySlam_1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
@@ -1543,7 +1536,7 @@
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>Size:1.25*{Size}</t>
+          <t>Size:0.75*{Size}</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -1553,17 +1546,17 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>火锥</t>
+          <t>地面打击</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Effect_PillarBlast_Ice_1</t>
+          <t>Effect_PillarBlast_Fire_1</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
@@ -1581,38 +1574,45 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>冰锥</t>
+          <t>火锥</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>900001</v>
+        <v>800002</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_1</t>
+          <t>Effect_PillarBlast_Ice_1</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Size:1.25*{Size}</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>StartPosition:{StartPosition}</t>
+        </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁1</t>
+          <t>冰锥</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_2</t>
+          <t>Effect_Thunder_1</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
@@ -1623,59 +1623,59 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁2</t>
+          <t>雷电连锁1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>900003</v>
+        <v>900002</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_3</t>
+          <t>Effect_Thunder_2</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>落雷(全局单例,深渊馈赠闪电)</t>
+          <t>雷电连锁2</t>
         </is>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>1000001</v>
+        <v>900003</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Effect_Mana_1</t>
+          <t>Effect_Thunder_3</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-魔王消耗魔力</t>
+          <t>落雷(全局单例,深渊馈赠闪电)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>1100001</v>
+        <v>1000001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>Effect_CreatureShow_1</t>
+          <t>Effect_Mana_1</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
@@ -1686,38 +1686,38 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-生成登场</t>
+          <t>放置魔物-魔王消耗魔力</t>
         </is>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>1200001</v>
+        <v>1100001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Effect_Blood_1</t>
+          <t>Effect_CreatureShow_1</t>
         </is>
       </c>
       <c r="C22" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>受击溅血(高频)</t>
+          <t>放置魔物-生成登场</t>
         </is>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="1">
       <c r="A23" s="0" t="n">
-        <v>1300001</v>
+        <v>1200001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>Effect_ShieldHit_1</t>
+          <t>Effect_Blood_1</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>护盾打击(高频)</t>
+          <t>受击溅血(高频)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="12" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>1400001</v>
+        <v>1300001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Effect_Move_1</t>
+          <t>Effect_ShieldHit_1</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
@@ -1749,112 +1749,133 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>进阶增加进度</t>
+          <t>护盾打击(高频)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="12" customHeight="1" s="1">
       <c r="A25" s="0" t="n">
-        <v>1500001</v>
+        <v>1400001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Effect_AscendComplete_1</t>
+          <t>Effect_Move_1</t>
         </is>
       </c>
       <c r="C25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>进阶完成庆祝</t>
+          <t>进阶增加进度</t>
         </is>
       </c>
     </row>
     <row r="26" ht="12" customHeight="1" s="1">
       <c r="A26" s="0" t="n">
-        <v>1600001</v>
+        <v>1500001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>Effect_Trail_1</t>
+          <t>Effect_AscendComplete_1</t>
         </is>
       </c>
       <c r="C26" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>攻击弹道拖尾(方案2 VFX)</t>
+          <t>进阶完成庆祝</t>
         </is>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>1700001</v>
+        <v>1600001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Effect_Shockwave_1</t>
+          <t>Effect_Trail_1</t>
         </is>
       </c>
       <c r="C27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="0" t="n">
-        <v>4</v>
-      </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+          <t>攻击弹道拖尾(方案2 VFX)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>1800001</v>
+        <v>1700001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Effect_FloorFire_1</t>
+          <t>Effect_Shockwave_1</t>
         </is>
       </c>
       <c r="C28" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr"/>
-      <c r="F28" s="0" t="inlineStr"/>
-      <c r="G28" s="0" t="inlineStr"/>
-      <c r="H28" s="0" t="inlineStr"/>
-      <c r="I28" s="0" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowEnduringSingletonEffect(effect_hit击中粒子1800001)按燃烧时长重设主粒子duration)</t>
+          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Effect_FloorFire_1</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr"/>
+      <c r="F29" s="0" t="inlineStr"/>
+      <c r="G29" s="0" t="inlineStr"/>
+      <c r="H29" s="0" t="inlineStr"/>
+      <c r="I29" s="0" t="inlineStr"/>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowEnduringSingletonEffect(effect_hit击中粒子1800001)按燃烧时长重设主粒子duration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
         <v>1900001</v>
       </c>
-      <c r="B29" s="0" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Effect_Hit_1</t>
         </is>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C30" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="0" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>击中(通用,牛头人投手落点)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1881,6 +1881,42 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="0" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Boom_Fire_2</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>火爆发(火大魔法师BOSS技能击中,全局单例)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>2000002</v>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Boom_Water_2</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>水爆发(水大魔法师BOSS技能击中,全局单例)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
